--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-16).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-16).xlsx
@@ -938,19 +938,19 @@
     <t>215</t>
   </si>
   <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R$ 8.840,34</t>
-  </si>
-  <si>
-    <t>94.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
-    <t>6.03</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 8.818,92</t>
+  </si>
+  <si>
+    <t>93.8</t>
+  </si>
+  <si>
+    <t>62.7</t>
+  </si>
+  <si>
+    <t>6.05</t>
   </si>
   <si>
     <t>20.0</t>
@@ -959,13 +959,13 @@
     <t>7.6</t>
   </si>
   <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>35.2%</t>
-  </si>
-  <si>
-    <t>19.0%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>34.3%</t>
+  </si>
+  <si>
+    <t>18.7%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -974,58 +974,58 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>4.1%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
+    <t>4.0%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>6.7%</t>
+    <t>6.6%</t>
   </si>
   <si>
     <t>2.4%</t>
   </si>
   <si>
-    <t>7.4%</t>
-  </si>
-  <si>
-    <t>2663.0</t>
-  </si>
-  <si>
-    <t>2160.0</t>
-  </si>
-  <si>
-    <t>114.0</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>462.0</t>
-  </si>
-  <si>
-    <t>130.0</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>762.0</t>
-  </si>
-  <si>
-    <t>268.0</t>
-  </si>
-  <si>
-    <t>843.0</t>
+    <t>7.2%</t>
+  </si>
+  <si>
+    <t>2719.0</t>
+  </si>
+  <si>
+    <t>2198.0</t>
+  </si>
+  <si>
+    <t>116.0</t>
+  </si>
+  <si>
+    <t>31.0</t>
+  </si>
+  <si>
+    <t>474.0</t>
+  </si>
+  <si>
+    <t>136.0</t>
+  </si>
+  <si>
+    <t>19.0</t>
+  </si>
+  <si>
+    <t>779.0</t>
+  </si>
+  <si>
+    <t>277.0</t>
+  </si>
+  <si>
+    <t>849.0</t>
   </si>
   <si>
     <t>0.6%</t>
   </si>
   <si>
-    <t>66.0</t>
+    <t>69.0</t>
   </si>
   <si>
     <t>1</t>
@@ -7728,7 +7728,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7758,35 +7758,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>9300.9500000000007</v>
+      </c>
+      <c r="N42" s="6">
+        <v>89</v>
+      </c>
+      <c r="O42" s="6">
+        <v>62</v>
+      </c>
+      <c r="P42" s="7">
+        <v>9.0760540229885063</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>34.991666129032254</v>
+      </c>
+      <c r="R42" s="8">
+        <v>17.965322580645161</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9367,7 +9425,9 @@
       <c r="N53" s="6">
         <v>88</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>47</v>
+      </c>
       <c r="P53" s="7">
         <v>5.2000000000000002</v>
       </c>
@@ -9377,31 +9437,75 @@
       <c r="R53" s="8">
         <v>6.7553191489361701</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.44680851063829785</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0.042553191489361701</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0.085106382978723402</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -14049,7 +14153,7 @@
         <v>19687</v>
       </c>
       <c r="B85" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C85" s="4">
         <v>51</v>
@@ -14079,35 +14183,93 @@
         <v>58</v>
       </c>
       <c r="L85" s="4"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="6"/>
-      <c r="O85" s="6"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="8"/>
-      <c r="R85" s="8"/>
-      <c r="S85" s="8"/>
-      <c r="T85" s="9"/>
-      <c r="U85" s="9"/>
-      <c r="V85" s="9"/>
-      <c r="W85" s="9"/>
-      <c r="X85" s="9"/>
-      <c r="Y85" s="9"/>
-      <c r="Z85" s="9"/>
-      <c r="AA85" s="9"/>
-      <c r="AB85" s="9"/>
-      <c r="AC85" s="9"/>
-      <c r="AD85" s="6"/>
-      <c r="AE85" s="6"/>
-      <c r="AF85" s="6"/>
-      <c r="AG85" s="6"/>
-      <c r="AH85" s="6"/>
-      <c r="AI85" s="6"/>
-      <c r="AJ85" s="6"/>
-      <c r="AK85" s="6"/>
-      <c r="AL85" s="6"/>
-      <c r="AM85" s="6"/>
-      <c r="AN85" s="9"/>
-      <c r="AO85" s="6"/>
+      <c r="M85" s="5">
+        <v>3859.4000000000001</v>
+      </c>
+      <c r="N85" s="6">
+        <v>57</v>
+      </c>
+      <c r="O85" s="6">
+        <v>12</v>
+      </c>
+      <c r="P85" s="7">
+        <v>6.2361780487804879</v>
+      </c>
+      <c r="Q85" s="8">
+        <v>20.366666666666667</v>
+      </c>
+      <c r="R85" s="8">
+        <v>12.637499999999999</v>
+      </c>
+      <c r="S85" s="8">
+        <v>7</v>
+      </c>
+      <c r="T85" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="U85" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V85" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="W85" s="9">
+        <v>0</v>
+      </c>
+      <c r="X85" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Y85" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Z85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="AB85" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AC85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE85" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF85" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI85" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL85" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM85" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP85" s="4">
         <v>58</v>
       </c>
@@ -16591,7 +16753,7 @@
         <v>0.04878048780487805</v>
       </c>
       <c r="W102" s="9">
-        <v>0</v>
+        <v>0.048780487804000003</v>
       </c>
       <c r="X102" s="9">
         <v>0.04878048780487805</v>
@@ -16621,7 +16783,7 @@
         <v>2</v>
       </c>
       <c r="AG102" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH102" s="6">
         <v>2</v>
@@ -18576,33 +18738,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>27</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.18518518518518517</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -25452,7 +25660,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -25482,35 +25690,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>9397.1499999999996</v>
+      </c>
+      <c r="N162" s="6">
+        <v>100</v>
+      </c>
+      <c r="O162" s="6">
+        <v>37</v>
+      </c>
+      <c r="P162" s="7">
+        <v>7.5370563829787232</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>18.100899999999999</v>
+      </c>
+      <c r="R162" s="8">
+        <v>1.8792783783783782</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.1891891891891892</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -25587,7 +25853,9 @@
       <c r="N163" s="6">
         <v>194</v>
       </c>
-      <c r="O163" s="6"/>
+      <c r="O163" s="6">
+        <v>150</v>
+      </c>
       <c r="P163" s="7">
         <v>4.926595744680851</v>
       </c>
@@ -25597,31 +25865,75 @@
       <c r="R163" s="8">
         <v>6.6968531468531465</v>
       </c>
-      <c r="S163" s="8"/>
+      <c r="S163" s="8">
+        <v>8</v>
+      </c>
       <c r="T163" s="9">
         <v>0.22</v>
       </c>
-      <c r="U163" s="9"/>
-      <c r="V163" s="9"/>
-      <c r="W163" s="9"/>
-      <c r="X163" s="9"/>
-      <c r="Y163" s="9"/>
-      <c r="Z163" s="9"/>
-      <c r="AA163" s="9"/>
-      <c r="AB163" s="9"/>
-      <c r="AC163" s="9"/>
-      <c r="AD163" s="6"/>
-      <c r="AE163" s="6"/>
-      <c r="AF163" s="6"/>
-      <c r="AG163" s="6"/>
-      <c r="AH163" s="6"/>
-      <c r="AI163" s="6"/>
-      <c r="AJ163" s="6"/>
-      <c r="AK163" s="6"/>
-      <c r="AL163" s="6"/>
-      <c r="AM163" s="6"/>
-      <c r="AN163" s="9"/>
-      <c r="AO163" s="6"/>
+      <c r="U163" s="9">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="V163" s="9">
+        <v>0.0066666666666666671</v>
+      </c>
+      <c r="W163" s="9">
+        <v>0</v>
+      </c>
+      <c r="X163" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="Y163" s="9">
+        <v>0.026666666666666668</v>
+      </c>
+      <c r="Z163" s="9">
+        <v>0.0066666666666666671</v>
+      </c>
+      <c r="AA163" s="9">
+        <v>0.046666666666666669</v>
+      </c>
+      <c r="AB163" s="9">
+        <v>0.053333333333333337</v>
+      </c>
+      <c r="AC163" s="9">
+        <v>0.013333333333333334</v>
+      </c>
+      <c r="AD163" s="6">
+        <v>34</v>
+      </c>
+      <c r="AE163" s="6">
+        <v>21</v>
+      </c>
+      <c r="AF163" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG163" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH163" s="6">
+        <v>10</v>
+      </c>
+      <c r="AI163" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ163" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK163" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL163" s="6">
+        <v>8</v>
+      </c>
+      <c r="AM163" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN163" s="9">
+        <v>0.0066666666666666671</v>
+      </c>
+      <c r="AO163" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP163" s="4">
         <v>58</v>
       </c>
@@ -28835,7 +29147,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>51</v>
@@ -31543,7 +31855,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>51</v>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-16).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-16).xlsx
@@ -938,34 +938,34 @@
     <t>215</t>
   </si>
   <si>
-    <t>29</t>
+    <t>23</t>
   </si>
   <si>
-    <t>R$ 8.818,92</t>
+    <t>R$ 8.832,27</t>
   </si>
   <si>
-    <t>93.8</t>
+    <t>93.3</t>
   </si>
   <si>
-    <t>62.7</t>
+    <t>63.2</t>
   </si>
   <si>
-    <t>6.05</t>
+    <t>6.12</t>
   </si>
   <si>
     <t>20.0</t>
   </si>
   <si>
-    <t>7.6</t>
+    <t>7.5</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.5</t>
   </si>
   <si>
-    <t>34.3%</t>
+    <t>34.0%</t>
   </si>
   <si>
-    <t>18.7%</t>
+    <t>18.2%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -974,49 +974,49 @@
     <t>0.3%</t>
   </si>
   <si>
-    <t>4.0%</t>
+    <t>3.9%</t>
   </si>
   <si>
-    <t>1.2%</t>
+    <t>1.1%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>6.6%</t>
+    <t>6.5%</t>
   </si>
   <si>
-    <t>2.4%</t>
+    <t>2.3%</t>
   </si>
   <si>
-    <t>7.2%</t>
+    <t>7.0%</t>
   </si>
   <si>
-    <t>2719.0</t>
+    <t>2741.0</t>
   </si>
   <si>
-    <t>2198.0</t>
+    <t>2217.0</t>
   </si>
   <si>
-    <t>116.0</t>
+    <t>120.0</t>
   </si>
   <si>
-    <t>31.0</t>
+    <t>32.0</t>
   </si>
   <si>
-    <t>474.0</t>
+    <t>479.0</t>
   </si>
   <si>
-    <t>136.0</t>
+    <t>137.0</t>
   </si>
   <si>
-    <t>19.0</t>
+    <t>21.0</t>
   </si>
   <si>
-    <t>779.0</t>
+    <t>787.0</t>
   </si>
   <si>
-    <t>277.0</t>
+    <t>279.0</t>
   </si>
   <si>
     <t>849.0</t>
@@ -2212,7 +2212,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2242,35 +2242,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>15289.34</v>
+      </c>
+      <c r="N6" s="6">
+        <v>145</v>
+      </c>
+      <c r="O6" s="6">
+        <v>117</v>
+      </c>
+      <c r="P6" s="7">
+        <v>9.7917808219178077</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>18.661965811965811</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.9975149122807019</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.25641025641025639</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.042735042735042736</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0.0085470085470085479</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -9135,7 +9193,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9165,8 +9223,12 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>0</v>
+      </c>
+      <c r="N51" s="6">
+        <v>0</v>
+      </c>
       <c r="O51" s="6"/>
       <c r="P51" s="7"/>
       <c r="Q51" s="8"/>
@@ -10204,33 +10266,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>96</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.052083333333333336</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0.010416666666</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.010416666666666666</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -24115,7 +24223,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -24145,35 +24253,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>7175.1199999999999</v>
+      </c>
+      <c r="N151" s="6">
+        <v>77</v>
+      </c>
+      <c r="O151" s="6">
+        <v>64</v>
+      </c>
+      <c r="P151" s="7">
+        <v>5.836363636363636</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>15.017707812499999</v>
+      </c>
+      <c r="R151" s="8">
+        <v>2.0888015625</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.53125</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0.015625</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -24997,7 +25163,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -25027,35 +25193,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>7125.9099999999999</v>
+      </c>
+      <c r="N157" s="6">
+        <v>69</v>
+      </c>
+      <c r="O157" s="6">
+        <v>57</v>
+      </c>
+      <c r="P157" s="7">
+        <v>7.8401955882352938</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>18.675731578947367</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.450584210526316</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.26315789473684209</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -25096,7 +25320,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25126,35 +25350,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>7934.8999999999996</v>
+      </c>
+      <c r="N158" s="6">
+        <v>77</v>
+      </c>
+      <c r="O158" s="6">
+        <v>63</v>
+      </c>
+      <c r="P158" s="7">
+        <v>7.8982688311688314</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>19.94126984126984</v>
+      </c>
+      <c r="R158" s="8">
+        <v>4.8053758064516128</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.063492063492063489</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0.031746031746031744</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -26131,7 +26413,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -26161,35 +26443,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>9106.9899999999998</v>
+      </c>
+      <c r="N165" s="6">
+        <v>98</v>
+      </c>
+      <c r="O165" s="6">
+        <v>70</v>
+      </c>
+      <c r="P165" s="7">
+        <v>12.884375</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>27.520952857142856</v>
+      </c>
+      <c r="R165" s="8">
+        <v>5.1123814285714282</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
